--- a/output/中钢协_上海长三角产业研学考察计划_排期表.xlsx
+++ b/output/中钢协_上海长三角产业研学考察计划_排期表.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="第三期排期" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="第四期排期" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合作框架" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="对价与分成落位" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -118,8 +119,30 @@
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00B03A2E"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00E88A1A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="005A636E"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="005A636E"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -161,6 +184,26 @@
         <fgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B03A2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E6DA4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E7D53"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5E1DE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -188,7 +231,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -308,7 +351,53 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -676,109 +765,133 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:C11"/>
+  <dimension ref="B2:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="90" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="96" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>钢铁 × 地产 × 产业园区</t>
+          <t>钢铁 × 不动产 × 产业园区</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>上海 / 长三角产业研学考察计划 与 合作框架</t>
+          <t>上海 / 长三角产业研学考察计划 与 联合主办合作框架</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>主办三方</t>
+          <t>联合主办（乙方）</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>中钢协流通分会 · 复旦大学住房政策研究中心（房地产研究中心） · 上海市杨浦区科技企业联合会</t>
+          <t>复旦大学住房政策研究中心 · 上海市科技企业联合会 · 上海市杨浦区科技企业联合会</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>形式</t>
+          <t>战略合作（甲方）</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>四期 · 每期两天半（2.5 天） · 上海（长三角延伸）</t>
+          <t>中国钢铁工业协会（总会层面）</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>规模</t>
+          <t>合作层级</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>每期 10–15 人 · 小规模高质量闭门</t>
+          <t>总会对总会 · 商务对商务 · 对等交流</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>保障</t>
+          <t>形式</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>主办方统一安排考察用车、工作餐与会务（费用计入组织成本）</t>
+          <t>四期 · 每期两天半（2.5 天） · 上海（长三角延伸）</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>考察内容</t>
+          <t>规模</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>标杆项目（房地产标杆项目，非房企） · 标杆园区 · 智能制造 · 科技企业 · 供需闭门撮合</t>
+          <t>每期 10–15 人 · 小规模高质量闭门</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>战略目标</t>
+          <t>成本口径</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>面向未来，成为中钢协在上海及长三角区域统筹的【总战略合作伙伴】</t>
+          <t>会务与接待等直接运营成本可各自独立核算；品牌与资源赋能须按对价回流</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="B11" s="3" t="inlineStr">
         <is>
+          <t>考察内容</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>不动产标杆项目（考察项目本身，非开发企业） · 标杆园区 · 智能制造 · 科技企业 · 供需闭门撮合</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>战略目标</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>面向未来，成为中国钢铁工业协会在上海及长三角区域统筹的【总战略合作伙伴】</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>本表结构</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>四期总览 → 各期排期（时间节点） → 合作框架</t>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>四期总览 → 各期排期（时间节点） → 合作框架（对等） → 对价与分成落位</t>
         </is>
       </c>
     </row>
@@ -857,12 +970,12 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>地产标杆 × 城市更新（存量盘活）</t>
+          <t>不动产标杆 × 城市更新（存量盘活）</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>对接烂尾楼盘、闲置地产（特殊资产重整）——帮房企盘活项目，钢材采购为配套</t>
+          <t>对接烂尾楼盘、闲置不动产（特殊资产重整）——帮不动产项目方盘活项目，钢材采购为配套</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
@@ -872,7 +985,7 @@
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>《存量时代地产项目盘活与建材成本重构》— 复旦大学住房政策研究中心</t>
+          <t>《存量时代不动产项目盘活与建材成本重构》— 复旦大学住房政策研究中心</t>
         </is>
       </c>
     </row>
@@ -904,7 +1017,7 @@
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <t>《城市更新与园区存量改造中的产业协同》— 复旦 + 杨浦区科技企业联合会</t>
+          <t>《城市更新与园区存量改造中的产业协同》— 复旦大学住房政策研究中心 + 上海市科技企业联合会</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1186,7 @@
       </c>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t>老工业厂房 → 双创示范园区，杨浦科企联合会资源</t>
+          <t>老工业厂房 → 双创示范园区，上海市杨浦区科技企业联合会资源</t>
         </is>
       </c>
     </row>
@@ -1404,14 +1517,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="31" t="inlineStr">
         <is>
-          <t>第一期 · 8月底 / 9月初 · 地产标杆 × 城市更新（存量盘活）（两天半）</t>
+          <t>第一期 · 8月底 / 9月初 · 不动产标杆 × 城市更新（存量盘活）（两天半）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="32" t="inlineStr">
         <is>
-          <t>聚焦：对接烂尾楼盘、闲置地产（特殊资产重整）——帮房企盘活项目，钢材采购为配套　|　用钢新场景：超高层与装配式建筑用钢、存量改造钢结构应用</t>
+          <t>聚焦：对接烂尾楼盘、闲置不动产（特殊资产重整）——帮不动产项目方盘活项目，钢材采购为配套　|　用钢新场景：超高层与装配式建筑用钢、存量改造钢结构应用</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1568,7 @@
       </c>
       <c r="D4" s="18" t="inlineStr">
         <is>
-          <t>主办三方致辞，发放行程与考察手册</t>
+          <t>联合主办与战略合作方致辞，发放行程与考察手册</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1590,7 @@
       </c>
       <c r="D5" s="18" t="inlineStr">
         <is>
-          <t>《存量时代地产项目盘活与建材成本重构》— 复旦大学住房政策研究中心</t>
+          <t>《存量时代不动产项目盘活与建材成本重构》— 复旦大学住房政策研究中心</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1634,7 @@
       </c>
       <c r="D7" s="18" t="inlineStr">
         <is>
-          <t>主办方统一安排</t>
+          <t>会务接待成本各自核算</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1744,7 @@
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>主办方统一安排</t>
+          <t>会务接待成本各自核算</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1788,7 @@
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>[标杆园区] 老工业厂房 → 双创示范园区，杨浦科企联合会资源</t>
+          <t>[标杆园区] 老工业厂房 → 双创示范园区，上海市杨浦区科技企业联合会资源</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1810,7 @@
       </c>
       <c r="D15" s="24" t="inlineStr">
         <is>
-          <t>供需端定向撮合</t>
+          <t>供需端定向撮合，纳入名单共管库</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1854,7 @@
       </c>
       <c r="D17" s="27" t="inlineStr">
         <is>
-          <t>形成交易线索，转入项目池跟踪</t>
+          <t>形成交易线索，转入项目池与分成落位</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1981,7 @@
       </c>
       <c r="D4" s="18" t="inlineStr">
         <is>
-          <t>主办三方致辞，发放行程与考察手册</t>
+          <t>联合主办与战略合作方致辞，发放行程与考察手册</t>
         </is>
       </c>
     </row>
@@ -1890,7 +2003,7 @@
       </c>
       <c r="D5" s="18" t="inlineStr">
         <is>
-          <t>《城市更新与园区存量改造中的产业协同》— 复旦 + 杨浦区科技企业联合会</t>
+          <t>《城市更新与园区存量改造中的产业协同》— 复旦大学住房政策研究中心 + 上海市科技企业联合会</t>
         </is>
       </c>
     </row>
@@ -1934,7 +2047,7 @@
       </c>
       <c r="D7" s="18" t="inlineStr">
         <is>
-          <t>主办方统一安排</t>
+          <t>会务接待成本各自核算</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2157,7 @@
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>主办方统一安排</t>
+          <t>会务接待成本各自核算</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2223,7 @@
       </c>
       <c r="D15" s="24" t="inlineStr">
         <is>
-          <t>供需端定向撮合</t>
+          <t>供需端定向撮合，纳入名单共管库</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2267,7 @@
       </c>
       <c r="D17" s="27" t="inlineStr">
         <is>
-          <t>形成交易线索，转入项目池跟踪</t>
+          <t>形成交易线索，转入项目池与分成落位</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2394,7 @@
       </c>
       <c r="D4" s="18" t="inlineStr">
         <is>
-          <t>主办三方致辞，发放行程与考察手册</t>
+          <t>联合主办与战略合作方致辞，发放行程与考察手册</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2460,7 @@
       </c>
       <c r="D7" s="18" t="inlineStr">
         <is>
-          <t>主办方统一安排</t>
+          <t>会务接待成本各自核算</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2570,7 @@
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>主办方统一安排</t>
+          <t>会务接待成本各自核算</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2636,7 @@
       </c>
       <c r="D15" s="24" t="inlineStr">
         <is>
-          <t>供需端定向撮合</t>
+          <t>供需端定向撮合，纳入名单共管库</t>
         </is>
       </c>
     </row>
@@ -2567,7 +2680,7 @@
       </c>
       <c r="D17" s="27" t="inlineStr">
         <is>
-          <t>形成交易线索，转入项目池跟踪</t>
+          <t>形成交易线索，转入项目池与分成落位</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2807,7 @@
       </c>
       <c r="D4" s="18" t="inlineStr">
         <is>
-          <t>主办三方致辞，发放行程与考察手册</t>
+          <t>联合主办与战略合作方致辞，发放行程与考察手册</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2873,7 @@
       </c>
       <c r="D7" s="18" t="inlineStr">
         <is>
-          <t>主办方统一安排</t>
+          <t>会务接待成本各自核算</t>
         </is>
       </c>
     </row>
@@ -2870,7 +2983,7 @@
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>主办方统一安排</t>
+          <t>会务接待成本各自核算</t>
         </is>
       </c>
     </row>
@@ -2936,7 +3049,7 @@
       </c>
       <c r="D15" s="24" t="inlineStr">
         <is>
-          <t>供需端定向撮合</t>
+          <t>供需端定向撮合，纳入名单共管库</t>
         </is>
       </c>
     </row>
@@ -2980,7 +3093,7 @@
       </c>
       <c r="D17" s="27" t="inlineStr">
         <is>
-          <t>形成交易线索，转入项目池跟踪</t>
+          <t>形成交易线索，转入项目池与分成落位</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:C33"/>
+  <dimension ref="B2:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3055,290 +3168,652 @@
     <row r="2">
       <c r="B2" s="39" t="inlineStr">
         <is>
-          <t>统筹合作框架</t>
+          <t>联合主办合作框架（对等 · 总会对总会 · 商务对商务）</t>
         </is>
       </c>
     </row>
     <row r="3" ht="44" customHeight="1">
       <c r="B3" s="40" t="inlineStr">
         <is>
-          <t>由中钢协流通分会、复旦大学房地产研究中心与杨浦区科技企业联合会三方合作，以“考察 + 对接 + 项目转化”闭环，服务钢铁产业链与地产 / 园区 / 制造业的跨产业撮合。</t>
+          <t>由中国钢铁工业协会（供给 / 渠道方）与复旦大学住房政策研究中心、上海市科技企业联合会、上海市杨浦区科技企业联合会（联合主办 / 平台赋能方）以对等结构合作，把学术公信力与真实买方网络转化为可量化、可定价的商业筹码。</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="B5" s="41" t="inlineStr">
         <is>
-          <t>一、两阶段合作设计</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="74" customHeight="1">
+          <t>一、合作层级与双方主体（对等）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
       <c r="B6" s="42" t="inlineStr">
         <is>
-          <t>阶段一 · 共建期（前 1–2 期，8–9 月）</t>
+          <t>甲方 · 供给 / 渠道方</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>• 前几次活动【不计营收】与中钢协共同开展，双方各自承担部分组织成本；
-• 目的：建立互信、验证模式、沉淀标杆案例、打磨供需撮合闭环；
-• 中钢协向协会会员收费、我方向自有校友 / 资源收费，各自收益归各自所有；
-• 以“真政策 + 真资源”降低门槛、精准筛选高质量决策人。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="74" customHeight="1">
+          <t>中国钢铁工业协会（总会层面）
+职责：上游钢铁企业资源 · 组织参与 · 协助邀约</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
       <c r="B7" s="42" t="inlineStr">
         <is>
-          <t>阶段二 · 盈利期（模式跑通后，10 月起）</t>
+          <t>乙方 · 联合主办 / 平台赋能方</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>• 一旦撮合 / 项目转化成功，按约定比例提取撮合服务费 / 项目服务费提成；
-• 以“产业咨询 / 项目服务费”名义，由复旦、杨浦联合会等正规主体开票；
-• 不做按成交额的居间分成账务，规避变相居间与合规风险；
-• 把“撮合位置”写进合作协议，服务费 / 项目费 / 会员制绑定，建立成交确认机制。</t>
+          <t>复旦大学住房政策研究中心 · 上海市科技企业联合会 · 上海市杨浦区科技企业联合会
+职责：品牌背书 · 需求端（买方 / 场景）资源 · 议程赋能 · 产品设计与规则</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="B9" s="41" t="inlineStr">
-        <is>
-          <t>二、盈利底线与分配原则（红线）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="40" customHeight="1">
-      <c r="B10" s="42" t="inlineStr">
-        <is>
-          <t>底线：不以亏损为合作前提</t>
+      <c r="B9" s="43" t="inlineStr">
+        <is>
+          <t>二、针对“各收各钱、自负盈亏”方案的指导性立场（红线）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="B10" s="44" t="inlineStr">
+        <is>
+          <t>红线 1</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>对方为会员制、有会费现金流；我方无会员制收入。组织成本（考察用车、工作餐、会务、专家、场地）须有明确分担或覆盖机制，我方不以亏损为合作前提。</t>
+          <t>仅“各自直接运营成本（会务、接待）”可独立核算；平台赋能层面必须有对价回流。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
-      <c r="B11" s="42" t="inlineStr">
-        <is>
-          <t>倾斜：向我方投入适当倾斜</t>
+      <c r="B11" s="44" t="inlineStr">
+        <is>
+          <t>红线 2</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>未来盈利分配应充分考虑我方投入的人力、财力与专业资源（复旦品牌、专业方案、政府与园区资源），在利润分配上向我方适当倾斜。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="40" customHeight="1">
-      <c r="B12" s="42" t="inlineStr">
-        <is>
-          <t>建议分配（可协商）</t>
+          <t>不接受“各收各钱”：对方有会员制沉淀长尾收益、我方无会员体系，各收各钱等于我方单向输出资源、拿不到产业链利润，属不对等。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="B12" s="44" t="inlineStr">
+        <is>
+          <t>红线 3</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>撮合 / 项目收益：主办方（复旦 + 杨浦）主导，中钢协取渠道分成；各自向自有客户的报名费归各自所有。需求入口、撮合规则与收费权不外放。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="B14" s="41" t="inlineStr">
-        <is>
-          <t>三、针对对方顾虑（痛点）的应对</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="B15" s="42" t="inlineStr">
-        <is>
-          <t>钢厂决策慢 / 中小钢厂动员难</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>初期不收费 + 真政策真资源，降低门槛、精准筛客，用小规模闭门锁定决策人。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="40" customHeight="1">
+          <t>定性升级：从“各自办活动” → “联合产品 / 联合主办合作”。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="B13" s="44" t="inlineStr">
+        <is>
+          <t>红线 4</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>对等交流、商务对商务、总会对总会；不以“免费 / 初期不计营收”开场。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="B15" s="41" t="inlineStr">
+        <is>
+          <t>三、我方核心商业资产界定</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="74" customHeight="1">
       <c r="B16" s="42" t="inlineStr">
         <is>
-          <t>地产 / 园区收缩、无预算</t>
+          <t>顶级信任背书（品牌资产）</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>商业模式转向存量盘活 / 特殊资产重整——帮房企盘活烂尾、闲置项目，钢材采购为配套，意愿强、订单大且持续。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
+          <t>复旦大学住房政策研究中心 + 上海市科技企业联合会 + 上海市杨浦区科技企业联合会 联合主办身份
+价值点：为上游钢企打通进入长三角核心圈层的“通行证”，大幅降低拓展大客户的信任成本与沟通门槛。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="57" customHeight="1">
       <c r="B17" s="42" t="inlineStr">
         <is>
-          <t>两边都怕被白嫖 / 跳单</t>
+          <t>高净值需求端资源（渠道资产）</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>撮合位置写进协议，服务费 / 项目费 / 会员制绑定，建立项目池与成交确认机制。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
+          <t>定向邀约不动产开发、城市更新、科技企业及新能源头部企业决策层
+价值点：上游产能渴望真实下游场景，我方掌握最稀缺的“买方 / 场景方”话语权——游学得以成立的根本前提。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="40" customHeight="1">
       <c r="B18" s="42" t="inlineStr">
         <is>
-          <t>抽成合规风险（国企审计严）</t>
+          <t>顶层战略视角与议程赋能（智力资产）</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>以咨询 / 项目服务费名义、正规主体开票，不走按成交额的第三方居间分成账。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="40" customHeight="1">
-      <c r="B19" s="42" t="inlineStr">
-        <is>
-          <t>钢厂不知产品新场景</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>第三、四期专程带钢厂销售 / 研发去发那科、特斯拉、光伏 / 储能企业，实地看智能装备与新能源到底要什么钢。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="B21" s="41" t="inlineStr">
-        <is>
-          <t>四、收费结构（初期让利，承接原报价逻辑）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
+          <t>空间资产运营、产业升级与科技赋能的深度洞察
+价值点：负责核心沙龙 / 闭门会的议题设置与主持，拉升整体活动的行业站位。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="B20" s="45" t="inlineStr">
+        <is>
+          <t>四、三种商业对价方案（三选一或组合）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="74" customHeight="1">
+      <c r="B21" s="42" t="inlineStr">
+        <is>
+          <t>方案 A · 品牌授权与平台赋能费（一次性买断制）</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>适用：对方希望完全主导后续转化、独享长尾收益
+• 单场品牌与资源服务费 3万–8万；或打包两天半 6万–15万（六位数级）
+• 含品牌在宣传物料 / 发文 / 现场呈现中的排他性使用权
+• 含核心嘉宾及精准企业群体的邀约成本</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="108" customHeight="1">
       <c r="B22" s="42" t="inlineStr">
         <is>
-          <t>基础游学套餐</t>
+          <t>方案 B · 增量收益与会员转化分成（深度绑定保底制）</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>阶段一成本价 / 减免；阶段二 9,800–16,800 元/人（分层报名，筛选机制）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
+          <t>适用：对方预算有限、愿共担风险共享增量
+• 前端收益分享：以联合主办名义收取的外部赞助费、席位费，我方抽取 30%–40% 渠道分成
+• 人头费：500–1500 元 / 人（可与前端分成叠加）
+• 后端资产保护（重点）：经本次游学首次接触并最终转化入会 / 购买其付费咨询·服务的企业，其首年会员费 / 服务费我方享 30%–50% 分佣</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="91" customHeight="1">
       <c r="B23" s="42" t="inlineStr">
         <is>
-          <t>产业撮合服务费</t>
+          <t>方案 C · 产业撮合 FA（居间）模式（长期利益制）</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>5 万–30 万 / 项目，或 成交金额的 1%–3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="B24" s="42" t="inlineStr">
-        <is>
-          <t>企业年度会员</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>10 万 / 30 万 每年（对方会员制为主，我方以项目 / 服务费为核心）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="B25" s="42" t="inlineStr">
-        <is>
-          <t>高阶专项项目</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>项目咨询费 + 成交分成（利润放大器）</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="B27" s="41" t="inlineStr">
-        <is>
-          <t>五、目标里程碑</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="B28" s="42" t="inlineStr">
-        <is>
-          <t>8–9 月</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>完成前两期共建，沉淀 ≥2 个标杆案例，建立项目池</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="B29" s="42" t="inlineStr">
-        <is>
-          <t>10–11 月</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>发那科 / 新能源专场跑通撮合闭环，落地 ≥1 个可收费项目</t>
+          <t>适用：活动直接指向大宗采购或深度供应链合作
+• 游学期间品牌及人力按成本价核算或予以免除，但须提前签署《资源对接与居间服务框架协议》
+• 本次活动及活动后一年内，由我方首配撮合达成的实质性采购订单 / 战略投资 / 技术合作，按行业标准提取居间佣金（建议成交额 1%–3%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="B25" s="46" t="inlineStr">
+        <is>
+          <t>五、对外沟通话术（可直接用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="108" customHeight="1">
+      <c r="B26" s="42" t="inlineStr">
+        <is>
+          <t>① 商业升维版（试水）</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>前期活动是基于双方资源互补的初步尝试，也验证了这个方向在钢铁产业与长三角资源对接上的可行性。从实际执行看，这类参访游学已不是简单的活动组织，而是涉及复旦品牌背书、政产学资源协调与高质量企业对接的系统性产品。基于此，后续若持续推进，建议升级为更标准化的联合主办合作模式，对双方也更可持续。具体而言，我方承担整体产品设计、复旦品牌及相关资源对接，因此每期活动建议设置基础的品牌与资源服务费；同时在招生或会员转化部分设计更合理的分成机制，确保双方投入与收益匹配。如您这边认可，我们可就下一期的合作模式与具体结构再细化对齐。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="108" customHeight="1">
+      <c r="B27" s="42" t="inlineStr">
+        <is>
+          <t>② 战略高位切入版（正式磋商）</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>这两天的行程，从会务与接待成本上，各自独立核算没有问题。但从产业逻辑看，中国钢铁工业协会带上游供应商来，核心痛点是找下游的去化场景；我方中心与科企联出面，等于用在长三角沉淀多年的学术公信力和真实买方网络，为钢铁企业做信任背书与精准导流。你们有成熟的会员体系，这是好事；但要确保这种高势能的品牌输出与资源对接在商业上形成良性闭环，而不是单向消耗。为让模式长期玩下去，我方梳理了一个联合主办合作框架——在收益分成或前端品牌费用上，看哪种模式更契合你们的预算与长期诉求。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="B29" s="43" t="inlineStr">
+        <is>
+          <t>六、我方底线</t>
         </is>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1">
-      <c r="B30" s="42" t="inlineStr">
-        <is>
-          <t>年底</t>
+      <c r="B30" s="44" t="inlineStr">
+        <is>
+          <t>底线 1</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>与中钢协签订【上海及长三角总战略合作伙伴】框架协议</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="24" customHeight="1">
-      <c r="B32" s="41" t="inlineStr">
-        <is>
-          <t>六、战略目标</t>
+          <t>不再接受“各收各钱”——对方有会员制、我方无，否则我方拿不到产业链利润；</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="B31" s="44" t="inlineStr">
+        <is>
+          <t>底线 2</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>品牌必须绑定收费——否则复旦 = 免费工具人；</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="B32" s="44" t="inlineStr">
+        <is>
+          <t>底线 3</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>我方必须参与产品定义（哪怕不参与招生）——否则被边缘化为执行方；</t>
         </is>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1">
-      <c r="B33" s="43" t="inlineStr">
-        <is>
-          <t>总战略合作伙伴</t>
+      <c r="B33" s="44" t="inlineStr">
+        <is>
+          <t>底线 4</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>面向未来，成为中钢协在上海及长三角区域统筹的【总战略合作伙伴】</t>
+          <t>坚持对等交流、商务对商务、总会对总会。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="B35" s="41" t="inlineStr">
+        <is>
+          <t>七、对方反应 · 分级应对</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="B36" s="47" t="inlineStr">
+        <is>
+          <t>接受</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>直接进入价格结构谈判，A / B / C 方案组合落位。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="B37" s="48" t="inlineStr">
+        <is>
+          <t>犹豫</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>给轻量版：先收基础品牌与资源服务费（方案 A 下限），保留后端分成条款。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="40" customHeight="1">
+      <c r="B38" s="49" t="inlineStr">
+        <is>
+          <t>拒绝</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>拒付品牌费 / 拒分成 / 坚持各收各 → 本质“要资源、不让参与收益”，降级为弱合作或退出。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="B40" s="41" t="inlineStr">
+        <is>
+          <t>八、目标里程碑</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="B41" s="42" t="inlineStr">
+        <is>
+          <t>下一期</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>以联合主办、对等结构落地，签署《联合主办合作框架与对价清单》</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="B42" s="42" t="inlineStr">
+        <is>
+          <t>中期</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>跑通会员转化分佣与撮合居间，形成清晰、可追溯的分成落位</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="B43" s="42" t="inlineStr">
+        <is>
+          <t>战略</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>与中国钢铁工业协会（总会）签订上海及长三角总战略合作伙伴框架协议</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="B44" s="50" t="inlineStr">
+        <is>
+          <t>战略目标</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>面向未来，成为中国钢铁工业协会在上海及长三角区域统筹的【总战略合作伙伴】</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="B21:C21"/>
+  <mergeCells count="9">
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B25:C25"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B40:C40"/>
     <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B35:C35"/>
+  </mergeCells>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>对价与分成落位（明确 · 可执行 · 可追溯）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>收益类型</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>计费方式</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>我方对价 / 分成</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>结算与凭证</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="B3" s="51" t="inlineStr">
+        <is>
+          <t>品牌与资源服务费</t>
+        </is>
+      </c>
+      <c r="C3" s="52" t="inlineStr">
+        <is>
+          <t>单场 / 打包固定</t>
+        </is>
+      </c>
+      <c r="D3" s="53" t="inlineStr">
+        <is>
+          <t>3–8万 / 场；6–15万 / 打包（预付）</t>
+        </is>
+      </c>
+      <c r="E3" s="54" t="inlineStr">
+        <is>
+          <t>活动前预付，正规主体开票</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="B4" s="42" t="inlineStr">
+        <is>
+          <t>报名 / 席位 / 赞助费</t>
+        </is>
+      </c>
+      <c r="C4" s="55" t="inlineStr">
+        <is>
+          <t>前端分成</t>
+        </is>
+      </c>
+      <c r="D4" s="56" t="inlineStr">
+        <is>
+          <t>30% – 40%</t>
+        </is>
+      </c>
+      <c r="E4" s="57" t="inlineStr">
+        <is>
+          <t>按场结算，凭报名与收款流水核对</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="B5" s="51" t="inlineStr">
+        <is>
+          <t>参会人头费</t>
+        </is>
+      </c>
+      <c r="C5" s="52" t="inlineStr">
+        <is>
+          <t>按实际参会人数</t>
+        </is>
+      </c>
+      <c r="D5" s="53" t="inlineStr">
+        <is>
+          <t>500 – 1500 元 / 人</t>
+        </is>
+      </c>
+      <c r="E5" s="54" t="inlineStr">
+        <is>
+          <t>按场结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="B6" s="42" t="inlineStr">
+        <is>
+          <t>会员转化分佣</t>
+        </is>
+      </c>
+      <c r="C6" s="55" t="inlineStr">
+        <is>
+          <t>后端分成</t>
+        </is>
+      </c>
+      <c r="D6" s="56" t="inlineStr">
+        <is>
+          <t>首年会费 / 服务费 30% – 50%</t>
+        </is>
+      </c>
+      <c r="E6" s="57" t="inlineStr">
+        <is>
+          <t>以名单共管库确认，转化后按季结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="B7" s="51" t="inlineStr">
+        <is>
+          <t>产业撮合居间佣金</t>
+        </is>
+      </c>
+      <c r="C7" s="52" t="inlineStr">
+        <is>
+          <t>按成交额比例</t>
+        </is>
+      </c>
+      <c r="D7" s="53" t="inlineStr">
+        <is>
+          <t>1% – 3%（活动后 1 年内首配撮合）</t>
+        </is>
+      </c>
+      <c r="E7" s="54" t="inlineStr">
+        <is>
+          <t>签居间协议，成交后结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>核心保护条款（数据与资源防火墙）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>条款</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="B11" s="42" t="inlineStr">
+        <is>
+          <t>1）名单共管与线索共享</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>游学期间产生的企业通讯录、需求表、合作意向库为双方共有数据资产，活动结束后双向同步交付。</t>
+        </is>
+      </c>
+      <c r="D11" s="58" t="n"/>
+      <c r="E11" s="58" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="B12" s="42" t="inlineStr">
+        <is>
+          <t>2）社群独立权</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>我方有权对邀请的买方 / 应用方企业建立独立“长三角产业协同专属群”；对方在群内二次营销需经我方审核或联合发起。</t>
+        </is>
+      </c>
+      <c r="D12" s="58" t="n"/>
+      <c r="E12" s="58" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="B13" s="42" t="inlineStr">
+        <is>
+          <t>3）品牌使用边界</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>复旦及科企联品牌授权仅限本次两天半活动特定周期；未经书面许可不得在常规运营或后续独立活动继续挂靠我方抬头。</t>
+        </is>
+      </c>
+      <c r="D13" s="58" t="n"/>
+      <c r="E13" s="58" t="n"/>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="B14" s="42" t="inlineStr">
+        <is>
+          <t>4）分佣确认与追溯</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>转化 / 成交以名单共管库为准，设活动后 1 年追溯期，防止跳单与资源洗单。</t>
+        </is>
+      </c>
+      <c r="D14" s="58" t="n"/>
+      <c r="E14" s="58" t="n"/>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="B16" s="59" t="inlineStr">
+        <is>
+          <t>说明：会务与接待等直接运营成本可各自独立核算；上述四类对价须约定于《联合主办合作框架与对价清单》，并以名单共管库作为分佣与追溯依据（活动后 1 年追溯期）。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C10:E10"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
